--- a/backend/assets/nakladnoy/warehouse/704-wh-7.0.4.xlsx
+++ b/backend/assets/nakladnoy/warehouse/704-wh-7.0.4.xlsx
@@ -3910,6 +3910,6 @@
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>